--- a/app/template/TOTAL_Todas_las_Dependencias.xlsx
+++ b/app/template/TOTAL_Todas_las_Dependencias.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="TITULO" sheetId="1" state="visible" r:id="rId3"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="71">
   <si>
     <t xml:space="preserve">FORMATO REQUERIMIENTOS </t>
   </si>
@@ -46,7 +46,7 @@
     <t xml:space="preserve">ANTEPROYECTO POA 2027</t>
   </si>
   <si>
-    <t xml:space="preserve">Recursos a presupuestar Por todas las dependencias.  Año 2027</t>
+    <t xml:space="preserve">Recursos a presupuestar Por todas las dependencias.  </t>
   </si>
   <si>
     <t xml:space="preserve">Requisición General de materiales y equipos de oficina (401).</t>
@@ -190,6 +190,9 @@
     <t xml:space="preserve">Cantidad Total</t>
   </si>
   <si>
+    <t xml:space="preserve">Recursos a presupuestar Por todas las dependencias. </t>
+  </si>
+  <si>
     <t xml:space="preserve">Requisición General de materiales y equipos de oficina (403).</t>
   </si>
   <si>
@@ -200,6 +203,9 @@
   </si>
   <si>
     <t xml:space="preserve">PRECIO UNIT EN $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recursos a presupuestar Por todas las dependencias.</t>
   </si>
   <si>
     <t xml:space="preserve">Requisición General de materiales y equipos de oficina (404)</t>
@@ -975,9 +981,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>657360</xdr:colOff>
+      <xdr:colOff>657000</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>169200</xdr:rowOff>
+      <xdr:rowOff>168840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -991,7 +997,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="498960" y="1539360"/>
-          <a:ext cx="992160" cy="725400"/>
+          <a:ext cx="1019160" cy="725040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1012,10 +1018,10 @@
       <xdr:rowOff>37800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>606600</xdr:colOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>498600</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>144000</xdr:rowOff>
+      <xdr:rowOff>143640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1029,7 +1035,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="240120" y="609480"/>
-          <a:ext cx="13046760" cy="677520"/>
+          <a:ext cx="13462200" cy="677160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1050,10 +1056,10 @@
       <xdr:rowOff>114840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>205560</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>612720</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>118800</xdr:rowOff>
+      <xdr:rowOff>118440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1062,8 +1068,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1614600" y="1638720"/>
-          <a:ext cx="11271240" cy="575640"/>
+          <a:off x="1641960" y="1638720"/>
+          <a:ext cx="10700640" cy="575280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1113,7 +1119,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -1141,7 +1147,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -1169,7 +1175,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -1197,7 +1203,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -1218,9 +1224,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1427040</xdr:colOff>
+      <xdr:colOff>1426680</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>99720</xdr:rowOff>
+      <xdr:rowOff>99360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1233,8 +1239,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="606960" y="1672560"/>
-          <a:ext cx="1236600" cy="819720"/>
+          <a:off x="621000" y="1672560"/>
+          <a:ext cx="1236240" cy="819360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1256,9 +1262,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>680760</xdr:colOff>
+      <xdr:colOff>680400</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>99720</xdr:rowOff>
+      <xdr:rowOff>99360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1267,8 +1273,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1830240" y="1387080"/>
-          <a:ext cx="11196360" cy="554760"/>
+          <a:off x="1844280" y="1387080"/>
+          <a:ext cx="11587680" cy="554400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1318,7 +1324,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -1346,7 +1352,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -1374,7 +1380,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -1402,7 +1408,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -1417,10 +1423,10 @@
       <xdr:rowOff>43560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>51120</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>836280</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>142560</xdr:rowOff>
+      <xdr:rowOff>142200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1434,7 +1440,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="417600"/>
-          <a:ext cx="13855320" cy="649440"/>
+          <a:ext cx="14308560" cy="649080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1461,9 +1467,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1298880</xdr:colOff>
+      <xdr:colOff>1298520</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>15480</xdr:rowOff>
+      <xdr:rowOff>15120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1476,8 +1482,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1245960" y="1374120"/>
-          <a:ext cx="960480" cy="736920"/>
+          <a:off x="1275120" y="1374120"/>
+          <a:ext cx="960120" cy="736560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1499,9 +1505,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>138600</xdr:colOff>
+      <xdr:colOff>138240</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>38520</xdr:rowOff>
+      <xdr:rowOff>38160</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1510,8 +1516,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2381400" y="1368000"/>
-          <a:ext cx="11119680" cy="575640"/>
+          <a:off x="2410560" y="1368000"/>
+          <a:ext cx="11528280" cy="575280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1561,7 +1567,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -1589,7 +1595,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -1617,7 +1623,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -1645,7 +1651,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -1660,10 +1666,10 @@
       <xdr:rowOff>1800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>721440</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>721080</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>51120</xdr:rowOff>
+      <xdr:rowOff>50760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1677,7 +1683,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="199800" y="382680"/>
-          <a:ext cx="15801120" cy="621000"/>
+          <a:ext cx="16301160" cy="620640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1704,9 +1710,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>945000</xdr:colOff>
+      <xdr:colOff>944640</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>169920</xdr:rowOff>
+      <xdr:rowOff>169560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1719,8 +1725,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="761040" y="1533960"/>
-          <a:ext cx="913680" cy="731520"/>
+          <a:off x="785160" y="1533960"/>
+          <a:ext cx="913320" cy="731160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1742,9 +1748,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>172440</xdr:colOff>
+      <xdr:colOff>172080</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>127080</xdr:rowOff>
+      <xdr:rowOff>126720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1753,8 +1759,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1720440" y="1647000"/>
-          <a:ext cx="11624400" cy="575640"/>
+          <a:off x="1744560" y="1647000"/>
+          <a:ext cx="12032280" cy="575280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1804,7 +1810,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -1832,7 +1838,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -1860,7 +1866,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -1888,7 +1894,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -1903,10 +1909,10 @@
       <xdr:rowOff>51840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>990000</xdr:colOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>128520</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>94320</xdr:rowOff>
+      <xdr:rowOff>93960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1920,7 +1926,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="114120" y="623520"/>
-          <a:ext cx="14590080" cy="613800"/>
+          <a:ext cx="15039720" cy="613440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1947,9 +1953,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>411480</xdr:colOff>
+      <xdr:colOff>411120</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>107640</xdr:rowOff>
+      <xdr:rowOff>107280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1963,7 +1969,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="253080" y="1270440"/>
-          <a:ext cx="992160" cy="932760"/>
+          <a:ext cx="1019160" cy="932400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1984,10 +1990,10 @@
       <xdr:rowOff>65160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>866880</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>791640</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>107280</xdr:rowOff>
+      <xdr:rowOff>106920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2001,7 +2007,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="149760" y="636840"/>
-          <a:ext cx="13700880" cy="613440"/>
+          <a:ext cx="14125320" cy="613080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2023,9 +2029,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>488160</xdr:colOff>
+      <xdr:colOff>487800</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>169920</xdr:rowOff>
+      <xdr:rowOff>169560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2034,8 +2040,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1325880" y="1499400"/>
-          <a:ext cx="11583360" cy="575640"/>
+          <a:off x="1353240" y="1499400"/>
+          <a:ext cx="12036960" cy="575280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2085,7 +2091,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -2113,7 +2119,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -2141,7 +2147,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -2169,7 +2175,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -2190,9 +2196,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>571680</xdr:colOff>
+      <xdr:colOff>571320</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>144360</xdr:rowOff>
+      <xdr:rowOff>144000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2206,7 +2212,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="413280" y="1503000"/>
-          <a:ext cx="794520" cy="736920"/>
+          <a:ext cx="814680" cy="736560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2227,10 +2233,10 @@
       <xdr:rowOff>60840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>825840</xdr:colOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>286560</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>102960</xdr:rowOff>
+      <xdr:rowOff>102600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2244,7 +2250,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="114480" y="632520"/>
-          <a:ext cx="13696560" cy="613440"/>
+          <a:ext cx="14119200" cy="613080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2265,10 +2271,10 @@
       <xdr:rowOff>123840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>607680</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>892800</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>127800</xdr:rowOff>
+      <xdr:rowOff>127440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2277,8 +2283,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1558080" y="1647720"/>
-          <a:ext cx="11201040" cy="575640"/>
+          <a:off x="1578600" y="1647720"/>
+          <a:ext cx="8924400" cy="575280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2328,7 +2334,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -2356,7 +2362,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -2384,7 +2390,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -2412,7 +2418,7 @@
           <a:endParaRPr lang="es-VE" sz="700" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="FreeSerif"/>
+            <a:latin typeface="DejaVu Serif"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -2658,7 +2664,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="49.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="10.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="9.42"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="2" width="9.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="6.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="7.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="7.13"/>
@@ -2672,10 +2678,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="5.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="2" width="7.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="2" width="7.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="2" width="9.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="2" width="10.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="2" width="9.42"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="32" min="32" style="2" width="10.76"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="18" min="18" style="2" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="19" min="19" style="2" width="10.49"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="20" min="20" style="2" width="9.42"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="31" min="22" style="0" width="10.76"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="32" min="32" style="2" width="10.76"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="36" min="33" style="0" width="10.76"/>
   </cols>
   <sheetData>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8169,8 +8177,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="2" width="6.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="2" width="9.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="2" width="9.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="19" width="9.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="19" width="11.16"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="19" min="18" style="19" width="9.82"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="20" min="20" style="19" width="11.16"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="36" min="22" style="0" width="10.76"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30100,10 +30109,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="53" width="7.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="53" width="7.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="53" width="9.28"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="18" min="18" style="53" width="10.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="53" width="8.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="53" width="13.05"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="18" min="18" style="53" width="10.76"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="19" min="19" style="53" width="8.22"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="20" min="20" style="53" width="13.05"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="2" width="16.81"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="36" min="22" style="0" width="10.76"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30232,7 +30242,7 @@
     <row r="14" s="30" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="59" t="s">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C14" s="59"/>
       <c r="D14" s="59"/>
@@ -30257,7 +30267,7 @@
     <row r="15" s="30" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
       <c r="B15" s="60" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15" s="60"/>
       <c r="D15" s="60"/>
@@ -30356,7 +30366,7 @@
       <c r="C19" s="63"/>
       <c r="D19" s="64"/>
       <c r="E19" s="65" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F19" s="65"/>
       <c r="G19" s="65"/>
@@ -30375,7 +30385,7 @@
       <c r="T19" s="67"/>
       <c r="U19" s="2"/>
     </row>
-    <row r="20" s="30" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" s="30" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
         <v>6</v>
       </c>
@@ -30386,7 +30396,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>10</v>
@@ -30431,7 +30441,7 @@
         <v>23</v>
       </c>
       <c r="S20" s="69" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T20" s="69" t="s">
         <v>25</v>
@@ -37780,8 +37790,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="19" width="6.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="19" width="5.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="19" width="6.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="19" width="14.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="19" style="19" width="10.49"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="18" min="18" style="19" width="14.93"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="20" min="19" style="19" width="10.49"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="36" min="22" style="0" width="10.76"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37923,7 +37934,7 @@
     <row r="14" s="30" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="5" t="s">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -37947,7 +37958,7 @@
     <row r="15" s="30" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="58"/>
       <c r="B15" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -37987,7 +37998,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="58" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -38031,7 +38042,7 @@
       <c r="C19" s="6"/>
       <c r="D19" s="20"/>
       <c r="E19" s="81" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F19" s="81"/>
       <c r="G19" s="81"/>
@@ -38049,7 +38060,7 @@
       <c r="S19" s="61"/>
       <c r="T19" s="61"/>
     </row>
-    <row r="20" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
         <v>6</v>
       </c>
@@ -41081,7 +41092,7 @@
       <c r="S155" s="71"/>
       <c r="T155" s="72"/>
       <c r="V155" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41106,7 +41117,7 @@
       <c r="S156" s="71"/>
       <c r="T156" s="71"/>
       <c r="V156" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="W156" s="2" t="s">
         <v>28</v>
@@ -44380,10 +44391,12 @@
   <sheetFormatPr defaultColWidth="10.765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="51.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.7"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="2" width="7.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="5" style="2" width="7.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="2" width="12.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="19" style="2" width="10.49"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="18" min="18" style="2" width="12.65"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="20" min="19" style="2" width="10.49"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="36" min="22" style="0" width="10.76"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44473,7 +44486,7 @@
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="58"/>
       <c r="B13" s="58" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C13" s="58"/>
       <c r="D13" s="58"/>
@@ -44508,7 +44521,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="94" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B15" s="94"/>
       <c r="C15" s="94"/>
@@ -44542,7 +44555,7 @@
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
@@ -49931,9 +49944,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="6.05"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="5.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="5.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="2" width="11.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="2" width="14.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="2" width="14.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="11.16"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="16" min="16" style="2" width="11.16"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="17" min="17" style="2" width="14.39"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="18" min="18" style="0" width="10.76"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="19" min="19" style="2" width="14.12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50026,7 +50041,7 @@
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="93"/>
       <c r="B14" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -50047,14 +50062,14 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="93" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
@@ -50071,7 +50086,7 @@
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
     </row>
-    <row r="17" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="95" t="s">
         <v>6</v>
       </c>
@@ -50118,7 +50133,7 @@
         <v>22</v>
       </c>
       <c r="P17" s="96" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q17" s="96" t="s">
         <v>23</v>
@@ -50135,54 +50150,54 @@
         <v>401</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C18" s="13" t="n">
-        <f aca="false">'4,01'!V78</f>
+        <f aca="false">'4,01'!V74</f>
         <v>0</v>
       </c>
       <c r="D18" s="13" t="n">
-        <f aca="false">'4,01'!W78</f>
+        <f aca="false">'4,01'!W74</f>
         <v>0</v>
       </c>
       <c r="E18" s="13" t="n">
-        <f aca="false">'4,01'!X78</f>
+        <f aca="false">'4,01'!X74</f>
         <v>0</v>
       </c>
       <c r="F18" s="13" t="n">
-        <f aca="false">'4,01'!Y78</f>
+        <f aca="false">'4,01'!Y74</f>
         <v>0</v>
       </c>
       <c r="G18" s="13" t="n">
-        <f aca="false">'4,01'!Z78</f>
+        <f aca="false">'4,01'!Z74</f>
         <v>0</v>
       </c>
       <c r="H18" s="13" t="n">
-        <f aca="false">'4,01'!AA78</f>
+        <f aca="false">'4,01'!AA74</f>
         <v>0</v>
       </c>
       <c r="I18" s="13" t="n">
-        <f aca="false">'4,01'!AB78</f>
+        <f aca="false">'4,01'!AB74</f>
         <v>0</v>
       </c>
       <c r="J18" s="13" t="n">
-        <f aca="false">'4,01'!AC78</f>
+        <f aca="false">'4,01'!AC74</f>
         <v>0</v>
       </c>
       <c r="K18" s="13" t="n">
-        <f aca="false">'4,01'!AD78</f>
+        <f aca="false">'4,01'!AD74</f>
         <v>0</v>
       </c>
       <c r="L18" s="13" t="n">
-        <f aca="false">'4,01'!AE78</f>
+        <f aca="false">'4,01'!AE74</f>
         <v>0</v>
       </c>
       <c r="M18" s="13" t="n">
-        <f aca="false">'4,01'!AF78</f>
+        <f aca="false">'4,01'!AF74</f>
         <v>0</v>
       </c>
       <c r="N18" s="13" t="n">
-        <f aca="false">'4,01'!AG78</f>
+        <f aca="false">'4,01'!AG74</f>
         <v>0</v>
       </c>
       <c r="O18" s="17" t="n">
@@ -50211,7 +50226,7 @@
         <v>402</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C19" s="14" t="n">
         <f aca="false">'4,02'!V792</f>
@@ -50287,7 +50302,7 @@
         <v>403</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C20" s="71" t="n">
         <f aca="false">'4,03'!V128</f>
@@ -50358,12 +50373,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="n">
         <v>404</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C21" s="71" t="n">
         <f aca="false">'4,04'!V157</f>
@@ -50434,12 +50449,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="n">
         <v>407</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C22" s="71" t="n">
         <f aca="false">'4,07'!V26</f>
@@ -50512,7 +50527,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="98" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B23" s="98"/>
       <c r="C23" s="72" t="n">
